--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>474074.3728512696</v>
+        <v>474074</v>
       </c>
       <c r="R2" t="n">
-        <v>6428614.889192338</v>
+        <v>6428615</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -748,19 +743,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1990-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -804,12 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>99398</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>474074.3728512696</v>
+        <v>474074</v>
       </c>
       <c r="R3" t="n">
-        <v>6428614.889192338</v>
+        <v>6428615</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>1986-01-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1986-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104048</v>
+        <v>104057</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101678</v>
+        <v>101684</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104057</v>
+        <v>104060</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101684</v>
+        <v>101685</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104060</v>
+        <v>104087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101685</v>
+        <v>101712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104087</v>
+        <v>104093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101712</v>
+        <v>101718</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104093</v>
+        <v>104100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101718</v>
+        <v>101725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104100</v>
+        <v>104104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101725</v>
+        <v>101729</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104104</v>
+        <v>104111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101729</v>
+        <v>101736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104114</v>
+        <v>104119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101739</v>
+        <v>101744</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104119</v>
+        <v>104127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101744</v>
+        <v>101752</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>74153978</v>
       </c>
       <c r="B2" t="n">
-        <v>104127</v>
+        <v>104137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>74552083</v>
       </c>
       <c r="B3" t="n">
-        <v>101752</v>
+        <v>101762</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -675,38 +675,38 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74153978</v>
+        <v>74552083</v>
       </c>
       <c r="B2" t="n">
-        <v>104137</v>
+        <v>102240</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>221235</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Anneberg 700 m NNO, Sm</t>
+          <t>Anneberg 750 m NNO, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
@@ -745,12 +745,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1990-12-31</t>
+          <t>1986-12-31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E6f 1114. SOM: Daphne mezereum. LEG: Jörgen Josefsson</t>
+          <t>Smålands flora 2007: KOO: 7E6f 1114. SOM: Lathyrus vernus. LEG: Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -764,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Fuktig lövskog</t>
+          <t>Stenig, frisk lövskog</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74552083</v>
+        <v>74153978</v>
       </c>
       <c r="B3" t="n">
-        <v>101762</v>
+        <v>104627</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,27 +797,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221235</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Anneberg 750 m NNO, Sm</t>
+          <t>Anneberg 700 m NNO, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
@@ -856,12 +856,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1986-12-31</t>
+          <t>1990-12-31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Smålands flora 2007: KOO: 7E6f 1114. SOM: Lathyrus vernus. LEG: Jörgen Josefsson</t>
+          <t>Smålands flora 2007: KOO: 7E6f 1114. SOM: Daphne mezereum. LEG: Jörgen Josefsson</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -875,7 +875,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Stenig, frisk lövskog</t>
+          <t>Fuktig lövskog</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>

--- a/artfynd/A 37016-2024 artfynd.xlsx
+++ b/artfynd/A 37016-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74552083</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,8 +904,17 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74153978</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>